--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-169</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.603.488,10</t>
-  </si>
-  <si>
-    <t>R$ 8.908,27
-R$ 9.096,00</t>
-  </si>
-  <si>
-    <t>(5.3%)
-(3.3%)</t>
+172</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.627.693,84</t>
+  </si>
+  <si>
+    <t>R$ 8.894,50
+R$ 9.078,08</t>
+  </si>
+  <si>
+    <t>(5.4%)
+(3.4%)</t>
   </si>
   <si>
     <t>97.2</t>
   </si>
   <si>
-    <t>(9.6%)</t>
-  </si>
-  <si>
-    <t>(43.9%)</t>
-  </si>
-  <si>
-    <t>(86.7%)</t>
+    <t>(9.5%)</t>
+  </si>
+  <si>
+    <t>(42.4%)</t>
+  </si>
+  <si>
+    <t>(85.0%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -950,10 +950,10 @@
     <t>29.3</t>
   </si>
   <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>14.9%</t>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -965,16 +965,16 @@
     <t>14.5</t>
   </si>
   <si>
-    <t>21.1</t>
+    <t>21.0</t>
   </si>
   <si>
     <t>64.0%</t>
   </si>
   <si>
-    <t>-R$ 49.962,51</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>-R$ 50.220,51</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>0.21649484536082464</v>
       </c>
       <c r="T7" s="6">
-        <v>0.33255816226875851</v>
+        <v>0.32417071710357492</v>
       </c>
       <c r="U7" s="6">
-        <v>0.023635232268391929</v>
+        <v>0.015247787103208359</v>
       </c>
       <c r="V7" s="6">
         <v>0.030735084976928721</v>
@@ -10886,7 +10886,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10920,25 +10920,59 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
+      <c r="O76" s="5">
+        <v>8665.1100000000006</v>
+      </c>
+      <c r="P76" s="5">
+        <v>8665.1100000000006</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.19713083312022595</v>
+      </c>
+      <c r="R76" s="7">
+        <v>111</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.15267175572519087</v>
+      </c>
+      <c r="T76" s="6">
+        <v>1.1431260653355813</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.78649239305675278</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.016093679133905973</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.0029320458713161172</v>
+      </c>
+      <c r="X76" s="8">
+        <v>25.89229125</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.1125</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.9853798245614036</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>5.4186863636363638</v>
+      </c>
       <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="AD76" s="8">
+        <v>15.71979125</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-71.799999999999997</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -16809,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -22924,7 +22958,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -22960,25 +22994,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>3205.3000000000002</v>
+      </c>
+      <c r="P172" s="5">
+        <v>3205.3000000000002</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>-0.15173632981003837</v>
+      </c>
+      <c r="R172" s="7">
+        <v>41</v>
+      </c>
+      <c r="S172" s="6">
+        <v>0.051282051282051322</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.28896724175584187</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0090121673478301568</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.04312997223348828</v>
+      </c>
+      <c r="W172" s="6">
+        <v>-0.008755966680185941</v>
+      </c>
+      <c r="X172" s="8">
+        <v>20.898275862068964</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>4.3780487804878048</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>3.9362068965517243</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>8.1965500000000002</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>15.160344827586206</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.93103448275862066</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>0</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -25851,7 +25921,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25887,25 +25957,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>12335.33</v>
+      </c>
+      <c r="P195" s="5">
+        <v>12335.33</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.061372080336876689</v>
+      </c>
+      <c r="R195" s="7">
+        <v>134</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.021897810218978075</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.31305048182740147</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0069490641920402609</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.018173206553857905</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0048375276543067757</v>
+      </c>
+      <c r="X195" s="8">
+        <v>29.744167000000001</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.6276083969465649</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>10.760999999999999</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.3825</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.53000000000000003</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-186.19999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.627.693,84</t>
-  </si>
-  <si>
-    <t>R$ 8.894,50
-R$ 9.078,08</t>
-  </si>
-  <si>
-    <t>(5.4%)
-(3.4%)</t>
-  </si>
-  <si>
-    <t>97.2</t>
-  </si>
-  <si>
-    <t>(9.5%)</t>
-  </si>
-  <si>
-    <t>(42.4%)</t>
-  </si>
-  <si>
-    <t>(85.0%)</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.647.236,83</t>
+  </si>
+  <si>
+    <t>R$ 8.903,98
+R$ 9.086,05</t>
+  </si>
+  <si>
+    <t>(5.7%)
+(3.7%)</t>
+  </si>
+  <si>
+    <t>97.4</t>
+  </si>
+  <si>
+    <t>(9.8%)</t>
+  </si>
+  <si>
+    <t>(41.5%)</t>
+  </si>
+  <si>
+    <t>(84.1%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,31 +947,31 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>6.6</t>
   </si>
   <si>
     <t>7.9</t>
   </si>
   <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>21.0</t>
-  </si>
-  <si>
-    <t>64.0%</t>
-  </si>
-  <si>
-    <t>-R$ 50.220,51</t>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>21.3</t>
+  </si>
+  <si>
+    <t>63.8%</t>
+  </si>
+  <si>
+    <t>-R$ 50.752,61</t>
   </si>
   <si>
     <t>2.95</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>9804.9599999999991</v>
+      </c>
+      <c r="P13" s="5">
+        <v>9804.9599999999991</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.30323405888246968</v>
+      </c>
+      <c r="R13" s="7">
+        <v>113</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.29813664596273293</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.40240450751456414</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.0027424997144302478</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.038532385649711981</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.036487502243762349</v>
+      </c>
+      <c r="X13" s="8">
+        <v>63.67307692307692</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.64835164835164838</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>26.487262601626018</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>16.371852222222223</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>46.794195000000002</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>53.51391978021978</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.27472527472527475</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-84.900000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -5646,10 +5682,10 @@
         <v>0.035714285714285809</v>
       </c>
       <c r="T34" s="6">
-        <v>0.28788521798086597</v>
+        <v>0.30534807131743069</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.050605691150593136</v>
+        <v>-0.033142837814028415</v>
       </c>
       <c r="V34" s="6">
         <v>0.057151555115783403</v>
@@ -8658,7 +8694,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8694,25 +8730,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>9738.0300000000007</v>
+      </c>
+      <c r="P58" s="5">
+        <v>9738.0300000000007</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.16650147389611847</v>
+      </c>
+      <c r="R58" s="7">
+        <v>115</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.21232876712328763</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.23016885345393265</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.12147413799300268</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.012061885206761531</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00029667191413458366</v>
+      </c>
+      <c r="X58" s="8">
+        <v>26.026907228915661</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.3493975903614458</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.1070567567567569</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>5.2524096385542167</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>9.6428560000000001</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>16.523695180722893</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.79518072289156627</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-447.19999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -10962,7 +11034,9 @@
       <c r="AB76" s="8">
         <v>5.4186863636363638</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>8.3176690000000004</v>
+      </c>
       <c r="AD76" s="8">
         <v>15.71979125</v>
       </c>
@@ -23949,7 +24023,9 @@
       <c r="AB179" s="8">
         <v>1.6966273809523809</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>10.384861000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>17.263529411764708</v>
       </c>
